--- a/src/CSV_protocol_config_files/module_3_test_2_AFFECTIVE_IMAGES.xlsx
+++ b/src/CSV_protocol_config_files/module_3_test_2_AFFECTIVE_IMAGES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akoun\Desktop\Biocruces\begibraintool\src\CSV_protocol_config_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E05001-DC04-4386-B418-4E8BA56D0CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180C337-5D95-4BD3-8DFC-10AFD8ECDCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t>arousal</t>
   </si>
@@ -42,87 +42,15 @@
     <t>EM0701_0800\EM0710.jpg</t>
   </si>
   <si>
-    <t>EM0501_0600\EM0579.jpg</t>
-  </si>
-  <si>
-    <t>EM0601_0700\EM0618.jpg</t>
-  </si>
-  <si>
-    <t>EM0801_0900\EM0819.jpg</t>
-  </si>
-  <si>
-    <t>EM0801_0900\EM0846.jpg</t>
-  </si>
-  <si>
     <t>EM0701_0800\EM0707.jpg</t>
   </si>
   <si>
-    <t>EM1001_1100\EM1066.jpg</t>
-  </si>
-  <si>
-    <t>EM0901_1000\EM0931.jpg</t>
-  </si>
-  <si>
-    <t>EM0201_0300\EM0284.jpg</t>
-  </si>
-  <si>
-    <t>EM0801_0900\EM0879.jpg</t>
-  </si>
-  <si>
-    <t>EM0301_0400\EM0369.jpg</t>
-  </si>
-  <si>
-    <t>EM0401_0500\EM0457.jpg</t>
-  </si>
-  <si>
-    <t>EM0201_0300\EM0269.jpg</t>
-  </si>
-  <si>
-    <t>EM0001_0100\EM0088.jpg</t>
-  </si>
-  <si>
-    <t>EM0701_0800\EM0792.jpg</t>
-  </si>
-  <si>
-    <t>EM0101_0200\EM0188.jpg</t>
-  </si>
-  <si>
-    <t>EM1001_1100\EM1091.jpg</t>
-  </si>
-  <si>
-    <t>EM0701_0800\EM0709.jpg</t>
-  </si>
-  <si>
-    <t>EM0401_0500\EM0449.jpg</t>
-  </si>
-  <si>
-    <t>EM0601_0700\EM0696.jpg</t>
-  </si>
-  <si>
     <t>EM0001_0100\EM0060.jpg</t>
   </si>
   <si>
-    <t>EM0301_0400\EM0305.jpg</t>
-  </si>
-  <si>
-    <t>EM0301_0400\EM0301.jpg</t>
-  </si>
-  <si>
     <t>EM0201_0300\EM0227.jpg</t>
   </si>
   <si>
-    <t>EM0001_0100\EM0065.jpg</t>
-  </si>
-  <si>
-    <t>EM1101_1202\EM1192.jpg</t>
-  </si>
-  <si>
-    <t>EM0601_0700\EM0689.jpg</t>
-  </si>
-  <si>
-    <t>EM0801_0900\EM0863.jpg</t>
-  </si>
-  <si>
     <t>affective_image_relative_path_1</t>
   </si>
   <si>
@@ -130,6 +58,21 @@
   </si>
   <si>
     <t>..\..\2.DATASETS\CEACO\</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>EM0401_0500\EM0459.jpg</t>
+  </si>
+  <si>
+    <t>EM0101_0200\EM0142.jpg</t>
+  </si>
+  <si>
+    <t>EM0501_0600\EM0525.jpg</t>
+  </si>
+  <si>
+    <t>EM0801_0900\EM0874.jpg</t>
   </si>
 </sst>
 </file>
@@ -145,12 +88,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -165,8 +114,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,10 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="27.86328125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -461,10 +412,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -475,10 +426,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -489,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -500,13 +451,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -514,349 +465,69 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
